--- a/Extracao.xlsx
+++ b/Extracao.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R504f04f1b10e45ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Rcff9ece72a4e4acc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1616,7 +1616,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>24462.569999999996</x:v>
+        <x:v>24462.57</x:v>
       </x:c>
       <x:c s="11"/>
       <x:c s="10"/>
@@ -1649,7 +1649,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>31329.239999999994</x:v>
+        <x:v>31329.239999999998</x:v>
       </x:c>
       <x:c s="11"/>
       <x:c s="10"/>
@@ -2045,7 +2045,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>107463.62999999999</x:v>
+        <x:v>107463.63</x:v>
       </x:c>
       <x:c s="11"/>
       <x:c s="10"/>
@@ -3200,7 +3200,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>19741.74</x:v>
+        <x:v>19741.739999999998</x:v>
       </x:c>
       <x:c s="11"/>
       <x:c s="10"/>
@@ -4784,7 +4784,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>1630.8400000000001</x:v>
+        <x:v>1630.84</x:v>
       </x:c>
       <x:c s="11"/>
       <x:c s="10"/>
@@ -6173,10 +6173,10 @@
         <x:v>36393.43</x:v>
       </x:c>
       <x:c s="11">
-        <x:v>0.57415308202606907</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>20895.4</x:v>
+        <x:v>0.57415308202606885</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>20895.399999999994</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7135,7 +7135,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>20256.73</x:v>
+        <x:v>20256.730000000003</x:v>
       </x:c>
       <x:c s="11"/>
       <x:c s="10"/>
@@ -8591,7 +8591,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>36050.109999999993</x:v>
+        <x:v>36050.11</x:v>
       </x:c>
       <x:c s="11"/>
       <x:c s="10"/>
@@ -9251,7 +9251,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>1545.0100000000002</x:v>
+        <x:v>1545.01</x:v>
       </x:c>
       <x:c s="11"/>
       <x:c s="10"/>
@@ -9944,10 +9944,10 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>149951.25000000003</x:v>
+        <x:v>149951.25</x:v>
       </x:c>
       <x:c s="11">
-        <x:v>0.1266735022215553</x:v>
+        <x:v>0.12667350222155532</x:v>
       </x:c>
       <x:c s="10">
         <x:v>18994.85</x:v>
@@ -11202,7 +11202,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>19570.039999999997</x:v>
+        <x:v>19570.04</x:v>
       </x:c>
       <x:c s="11"/>
       <x:c s="10"/>
@@ -12460,7 +12460,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>36908.439999999988</x:v>
+        <x:v>36908.44</x:v>
       </x:c>
       <x:c s="11"/>
       <x:c s="10"/>
@@ -14143,7 +14143,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>5382.28</x:v>
+        <x:v>5382.2799999999988</x:v>
       </x:c>
       <x:c s="11"/>
       <x:c s="10"/>
@@ -14704,7 +14704,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>16440.410000000003</x:v>
+        <x:v>16440.41</x:v>
       </x:c>
       <x:c s="11"/>
       <x:c s="10"/>
@@ -16061,10 +16061,10 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>252746.49000000002</x:v>
+        <x:v>252746.49</x:v>
       </x:c>
       <x:c s="11">
-        <x:v>0.31075248562304464</x:v>
+        <x:v>0.31075248562304469</x:v>
       </x:c>
       <x:c s="10">
         <x:v>78541.6</x:v>
@@ -16164,7 +16164,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>37911.97</x:v>
+        <x:v>37911.969999999994</x:v>
       </x:c>
       <x:c s="11"/>
       <x:c s="10"/>
@@ -18423,10 +18423,10 @@
         <x:v>102599.12999999999</x:v>
       </x:c>
       <x:c s="11">
-        <x:v>0.25301208694459687</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>25958.819999999996</x:v>
+        <x:v>0.25301208694459693</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>25958.82</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -19517,7 +19517,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>116757.17</x:v>
+        <x:v>116757.17000000001</x:v>
       </x:c>
       <x:c s="11"/>
       <x:c s="10"/>
@@ -20573,7 +20573,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>19564.63</x:v>
+        <x:v>19564.629999999997</x:v>
       </x:c>
       <x:c s="11"/>
       <x:c s="10"/>
@@ -27059,7 +27059,7 @@
       <x:c s="10"/>
       <x:c s="11"/>
       <x:c s="10">
-        <x:v>2946.39</x:v>
+        <x:v>2946.3899999999994</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -28280,7 +28280,7 @@
       <x:c s="10"/>
       <x:c s="11"/>
       <x:c s="10">
-        <x:v>3850.5299999999997</x:v>
+        <x:v>3850.5299999999993</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29303,7 +29303,7 @@
       <x:c s="10"/>
       <x:c s="11"/>
       <x:c s="10">
-        <x:v>11712.019999999999</x:v>
+        <x:v>11712.02</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29666,7 +29666,7 @@
       <x:c s="10"/>
       <x:c s="11"/>
       <x:c s="10">
-        <x:v>17584.800000000003</x:v>
+        <x:v>17584.8</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -29765,7 +29765,7 @@
       <x:c s="10"/>
       <x:c s="11"/>
       <x:c s="10">
-        <x:v>6421.42</x:v>
+        <x:v>6421.420000000001</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -30656,7 +30656,7 @@
       <x:c s="10"/>
       <x:c s="11"/>
       <x:c s="10">
-        <x:v>4269.26</x:v>
+        <x:v>4269.2599999999993</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31250,7 +31250,7 @@
       <x:c s="10"/>
       <x:c s="11"/>
       <x:c s="10">
-        <x:v>5500.28</x:v>
+        <x:v>5500.2800000000007</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31514,7 +31514,7 @@
       <x:c s="10"/>
       <x:c s="11"/>
       <x:c s="10">
-        <x:v>12588.550000000001</x:v>
+        <x:v>12588.55</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31613,7 +31613,7 @@
       <x:c s="10"/>
       <x:c s="11"/>
       <x:c s="10">
-        <x:v>72070.45</x:v>
+        <x:v>72070.450000000026</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31910,7 +31910,7 @@
       <x:c s="10"/>
       <x:c s="11"/>
       <x:c s="10">
-        <x:v>218.56</x:v>
+        <x:v>176.59</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -31976,7 +31976,7 @@
       <x:c s="10"/>
       <x:c s="11"/>
       <x:c s="10">
-        <x:v>11377.990000000002</x:v>
+        <x:v>11377.990000000003</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32340,6 +32340,1161 @@
       <x:c s="11"/>
       <x:c s="10">
         <x:v>3849.3500000000004</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DL - LED</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ESPIRITO SANTO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VILA VELHA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9680</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CAMPOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>3867.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DL - LED</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RIO GRANDE DO SUL</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ESTEIO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9945</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VENDAS TEC</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>28559.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DL - LED</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RIO GRANDE DO SUL</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>PASSO FUNDO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9945</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VENDAS TEC</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>38608.619999999995</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DL - LED</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SAO PAULO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SANTA BARBARA D OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9932</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>EDNALDO L</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>5745.48</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DP - Plástico</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ALAGOAS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ARAPIRACA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9560</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VASCONCELOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>6264.3499999999995</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DP - Plástico</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MATO GROSSO DO SUL</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>PONTA PORA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9792</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>LIGHT REPRES</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>6278.53</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DP - Plástico</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MINAS GERAIS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BELO HORIZONTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9640</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CACAJAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>49.13</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DP - Plástico</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>PARANA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Maringa</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9893</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SANTOS &amp; COR</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>1310.12</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DP - Plástico</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RIO GRANDE DO SUL</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>PAROBE</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9885</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>FOTOLUMEN</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>176.44</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DP - Plástico</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RIO GRANDE DO SUL</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>PORTO ALEGRE</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9885</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>FOTOLUMEN</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>3277</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DP - Plástico</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RIO GRANDE DO SUL</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RODEIO BONITO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9916</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>LAUDIR REP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>1486.1100000000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DP - Plástico</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SANTA CATARINA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BLUMENAU</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9795</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RJS REPRES</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>25780.690000000002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DP - Plástico</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SANTA CATARINA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JOINVILLE</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9520</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CAYMARK</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>606.13</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DP - Plástico</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SAO PAULO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CAJAMAR</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9963</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DANIEL ROCHA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>5116.8399999999992</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DP - Plástico</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SAO PAULO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SAO PAULO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9883</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CGK P. REPRE</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>5074.38</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DP - Plástico</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SAO PAULO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TAUBATE</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9290</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BOTELHO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>751.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DU - Aluminio</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ALAGOAS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ARAPIRACA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9560</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VASCONCELOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>87.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DU - Aluminio</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BAHIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Dias d'Ávila</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>7064</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>B C L</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>3602.6000000000004</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DU - Aluminio</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GOIAS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GOIANIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9939</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DECASTRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>5916.25</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DU - Aluminio</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MINAS GERAIS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BELO HORIZONTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9640</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CACAJAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>6090</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DU - Aluminio</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MINAS GERAIS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UBERABA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9958</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>KEYLA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>2750.17</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DU - Aluminio</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>PARANA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Maringa</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9893</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SANTOS &amp; COR</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>5955.89</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DU - Aluminio</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RIO GRANDE DO SUL</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>PANAMBI</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9916</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>LAUDIR REP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>41003.27</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DU - Aluminio</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RIO GRANDE DO SUL</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>PAROBE</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9885</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>FOTOLUMEN</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>4326.57</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DU - Aluminio</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RIO GRANDE DO SUL</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>PORTO ALEGRE</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9885</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>FOTOLUMEN</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>4114.49</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DU - Aluminio</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SANTA CATARINA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CRICIUMA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9960</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>J J SCHMIDT</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>6856.82</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DU - Aluminio</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SANTA CATARINA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RIO DO SUL</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9795</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RJS REPRES</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>2192.33</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DU - Aluminio</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SAO PAULO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CAJAMAR</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9963</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DANIEL ROCHA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>36526.42</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DX - EX</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MATO GROSSO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SORRISO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>8012</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REPAN</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>298.82</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46214</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DP - Plástico</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ALAGOAS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MACEIO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9560</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VASCONCELOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>9432.18</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46214</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DP - Plástico</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MINAS GERAIS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ARAXA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9860</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>LANJO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>1683.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46214</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DU - Aluminio</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ALAGOAS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MACEIO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9560</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VASCONCELOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>21290.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46214</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DU - Aluminio</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MINAS GERAIS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ARAXA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9860</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>LANJO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>14100.150000000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46214</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DU - Aluminio</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SAO PAULO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TAUBATE</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9290</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BOTELHO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>930.61</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>46215</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DP - Plástico</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>PARANA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CURITIBA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>9520</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CAYMARK</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10"/>
+      <x:c s="11"/>
+      <x:c s="10">
+        <x:v>3818.6400000000003</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -32354,13 +33509,13 @@
       <x:c s="12"/>
       <x:c s="1"/>
       <x:c s="13">
-        <x:v>12161713.389999993</x:v>
+        <x:v>12161713.389999995</x:v>
       </x:c>
       <x:c s="14">
-        <x:v>0.17871744385845967</x:v>
+        <x:v>0.20370446996695771</x:v>
       </x:c>
       <x:c s="13">
-        <x:v>2173510.330000001</x:v>
+        <x:v>2477395.3800000013</x:v>
       </x:c>
     </x:row>
     <x:row/>
